--- a/templates/schedule_template.xlsx
+++ b/templates/schedule_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuki0\Documents\VS code Projects\Weekly_Schedule\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C6A634-8D46-4970-9CD0-71A72CB004BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2E3A85-C415-42EB-B79B-DADAAFECB5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E01E9FA-DDC8-43E5-BEB2-CBC6E8589C87}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>曜日</t>
     <rPh sb="0" eb="2">
@@ -100,13 +100,6 @@
     <t>日付</t>
     <rPh sb="0" eb="2">
       <t>ヒヅケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>担任より</t>
-    <rPh sb="0" eb="2">
-      <t>タンニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -371,14 +364,14 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="UD Digi Kyokasho N-B"/>
       <family val="1"/>
       <charset val="128"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="UD Digi Kyokasho N-B"/>
       <family val="1"/>
@@ -883,7 +876,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -902,9 +895,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
@@ -955,14 +945,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -970,26 +972,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1325,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33E9C80-374C-4D3B-9A24-903857DA7744}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.296875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -1336,7 +1329,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1352,7 +1345,7 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -1397,23 +1390,23 @@
         <v>0</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>16</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>17</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -1432,71 +1425,71 @@
       <c r="A7" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="43"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:8" ht="45.3" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="22">
         <v>1</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="43"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:8" ht="45.3" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="22">
         <v>2</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="43"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="42"/>
     </row>
     <row r="10" spans="1:8" ht="45.3" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="22">
         <v>3</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="43"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="42"/>
     </row>
     <row r="11" spans="1:8" ht="45.3" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="22">
         <v>4</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="43"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="42"/>
     </row>
     <row r="12" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="52"/>
+      <c r="B12" s="45"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="52"/>
+      <c r="D12" s="45"/>
       <c r="E12" s="12"/>
-      <c r="F12" s="53"/>
+      <c r="F12" s="46"/>
       <c r="G12" s="3"/>
       <c r="H12" s="12"/>
     </row>
@@ -1504,11 +1497,11 @@
       <c r="A13" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="52"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="52"/>
+      <c r="D13" s="45"/>
       <c r="E13" s="12"/>
-      <c r="F13" s="53"/>
+      <c r="F13" s="46"/>
       <c r="G13" s="3"/>
       <c r="H13" s="12"/>
     </row>
@@ -1516,103 +1509,103 @@
       <c r="A14" s="22">
         <v>5</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="43"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="42"/>
     </row>
     <row r="15" spans="1:8" ht="45.3" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="22">
         <v>6</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="43"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="42"/>
     </row>
     <row r="16" spans="1:8" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="47"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="55"/>
     </row>
     <row r="17" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="25"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="35"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="34"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="30"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="26"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="38"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="37"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="31"/>
+      <c r="H18" s="30"/>
     </row>
     <row r="19" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="38"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="37"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="31"/>
+      <c r="H19" s="30"/>
     </row>
     <row r="20" spans="1:8" ht="15.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="26"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="38"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="37"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="31"/>
+      <c r="H20" s="30"/>
     </row>
     <row r="21" spans="1:8" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A21" s="27"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="41"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="40"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="32"/>
+      <c r="H21" s="31"/>
     </row>
     <row r="22" spans="1:8" ht="52.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="55"/>
-    </row>
-    <row r="23" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="47"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="48"/>
+    </row>
+    <row r="23" spans="1:8" ht="8.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="3"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1622,52 +1615,40 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="29" t="s">
+    <row r="24" spans="1:8" ht="70.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="51"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="53"/>
+    </row>
+    <row r="25" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="15"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" s="19" customFormat="1" ht="32.4" x14ac:dyDescent="0.45">
+      <c r="A26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" ht="53.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="51"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="50"/>
-    </row>
-    <row r="26" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="15"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" s="19" customFormat="1" ht="32.4" x14ac:dyDescent="0.45">
-      <c r="A27" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
